--- a/TextGame project/Assets/Resources/Story/4.xlsx
+++ b/TextGame project/Assets/Resources/Story/4.xlsx
@@ -187,7 +187,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,19 +205,6 @@
       <sz val="9.8"/>
       <color rgb="FFC9A26D"/>
       <name val="JetBrains Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -683,138 +670,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -822,9 +809,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1561,11 +1547,11 @@
         <v>45</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="B19" s="5"/>
+      <c r="B19" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TextGame project/Assets/Resources/Story/4.xlsx
+++ b/TextGame project/Assets/Resources/Story/4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFB8673-03C9-4A34-AD39-769B16517A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5C09CE-A822-4DF2-8EE0-D244D460596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -983,7 +983,7 @@
         <v>28</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:21">

--- a/TextGame project/Assets/Resources/Story/4.xlsx
+++ b/TextGame project/Assets/Resources/Story/4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5C09CE-A822-4DF2-8EE0-D244D460596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A262D2FB-4D8B-48B5-95A2-71B4F8A9B6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -155,16 +155,10 @@
     <t>（千叶追上林深，两人一起往楼上走）</t>
   </si>
   <si>
-    <t>喂，你还没说你叫什么名字呢。</t>
-  </si>
-  <si>
     <t>林深</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>林深。</t>
-  </si>
-  <si>
     <t>Linshen</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -173,43 +167,60 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>林深？我叫千叶！</t>
-  </si>
-  <si>
     <t>（嗯了一声，没再说什么）</t>
   </si>
   <si>
-    <t>林深，你说你来调查事情，到底调查什么啊？</t>
-  </si>
-  <si>
-    <t>你不需要知道。</t>
-  </si>
-  <si>
-    <t>什么嘛，这么神秘...</t>
-  </si>
-  <si>
     <t>（两人走到二楼，走廊里更暗了）</t>
   </si>
   <si>
-    <t>刚才的声音... 是从哪里传来的？</t>
-  </si>
-  <si>
-    <t>那边。</t>
-  </si>
-  <si>
     <t>（走廊尽头是旧图书馆的方向）</t>
   </si>
   <si>
-    <t>旧图书馆？听说那里最吓人了...</t>
-  </si>
-  <si>
-    <t>怕的话就回去。</t>
-  </si>
-  <si>
-    <t>谁、谁怕了！走就走！</t>
-  </si>
-  <si>
     <t>（两人往旧图书馆走去）</t>
+  </si>
+  <si>
+    <t>（小声）喂，你还没说你叫什么名字呢。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷淡）林深。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（微笑）林深？我叫千叶！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（好奇）林深，你说你来调查事情，到底调查什么啊？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（冷淡）你不需要知道。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（嘟嘴）什么嘛，这么神秘...</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（紧张）刚才的声音... 是从哪里传来的？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（指了指走廊尽头）那边。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（害怕）旧图书馆？听说那里最吓人了...</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（看了她一眼）怕的话就回去。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>（逞强）谁、谁怕了！走就走！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -659,6 +670,9 @@
       <c r="E2">
         <v>5</v>
       </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
       <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
@@ -675,7 +689,7 @@
         <v>819.16989999999998</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -683,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -691,6 +705,9 @@
       <c r="R3">
         <v>5</v>
       </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
       <c r="T3">
         <v>-640.83010000000002</v>
       </c>
@@ -700,16 +717,19 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="R4">
         <v>5</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
       </c>
       <c r="T4">
         <v>-640.83010000000002</v>
@@ -720,10 +740,10 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -731,6 +751,9 @@
       <c r="R5">
         <v>5</v>
       </c>
+      <c r="S5">
+        <v>2</v>
+      </c>
       <c r="T5">
         <v>-640.83010000000002</v>
       </c>
@@ -740,16 +763,19 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="R6">
         <v>5</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
       </c>
       <c r="T6">
         <v>-640.83010000000002</v>
@@ -760,10 +786,10 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -771,6 +797,9 @@
       <c r="R7">
         <v>5</v>
       </c>
+      <c r="S7">
+        <v>2</v>
+      </c>
       <c r="T7">
         <v>-640.83010000000002</v>
       </c>
@@ -780,16 +809,19 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="R8">
         <v>5</v>
+      </c>
+      <c r="S8">
+        <v>2</v>
       </c>
       <c r="T8">
         <v>-640.83010000000002</v>
@@ -800,16 +832,19 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="R9">
         <v>5</v>
+      </c>
+      <c r="S9">
+        <v>2</v>
       </c>
       <c r="T9">
         <v>-640.83010000000002</v>
@@ -823,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
@@ -831,6 +866,9 @@
       <c r="R10">
         <v>5</v>
       </c>
+      <c r="S10">
+        <v>2</v>
+      </c>
       <c r="T10">
         <v>-640.83010000000002</v>
       </c>
@@ -840,10 +878,10 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
@@ -851,6 +889,9 @@
       <c r="R11">
         <v>5</v>
       </c>
+      <c r="S11">
+        <v>2</v>
+      </c>
       <c r="T11">
         <v>-640.83010000000002</v>
       </c>
@@ -860,16 +901,19 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="R12">
         <v>5</v>
+      </c>
+      <c r="S12">
+        <v>2</v>
       </c>
       <c r="T12">
         <v>-640.83010000000002</v>
@@ -883,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>1</v>
@@ -891,6 +935,9 @@
       <c r="R13">
         <v>5</v>
       </c>
+      <c r="S13">
+        <v>2</v>
+      </c>
       <c r="T13">
         <v>-640.83010000000002</v>
       </c>
@@ -900,10 +947,10 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
@@ -911,6 +958,9 @@
       <c r="R14">
         <v>5</v>
       </c>
+      <c r="S14">
+        <v>2</v>
+      </c>
       <c r="T14">
         <v>-640.83010000000002</v>
       </c>
@@ -920,16 +970,19 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="R15">
         <v>5</v>
+      </c>
+      <c r="S15">
+        <v>2</v>
       </c>
       <c r="T15">
         <v>-640.83010000000002</v>
@@ -940,16 +993,19 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
         <v>3</v>
       </c>
       <c r="R16">
         <v>5</v>
+      </c>
+      <c r="S16">
+        <v>2</v>
       </c>
       <c r="T16">
         <v>-640.83010000000002</v>
@@ -963,13 +1019,16 @@
         <v>0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
         <v>1</v>
       </c>
       <c r="R17">
         <v>5</v>
+      </c>
+      <c r="S17">
+        <v>2</v>
       </c>
       <c r="T17">
         <v>-640.83010000000002</v>
@@ -983,7 +1042,7 @@
         <v>28</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:21">

--- a/TextGame project/Assets/Resources/Story/4.xlsx
+++ b/TextGame project/Assets/Resources/Story/4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A262D2FB-4D8B-48B5-95A2-71B4F8A9B6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25483265-63B9-4999-9CA1-4BF98258B93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -671,7 +671,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>21</v>
@@ -706,7 +706,7 @@
         <v>5</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3">
         <v>-640.83010000000002</v>
@@ -729,7 +729,7 @@
         <v>5</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>-640.83010000000002</v>
@@ -752,7 +752,7 @@
         <v>5</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>-640.83010000000002</v>
@@ -775,7 +775,7 @@
         <v>5</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>-640.83010000000002</v>
@@ -798,7 +798,7 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>-640.83010000000002</v>
@@ -821,7 +821,7 @@
         <v>5</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>-640.83010000000002</v>
@@ -844,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>-640.83010000000002</v>
@@ -867,7 +867,7 @@
         <v>5</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>-640.83010000000002</v>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>-640.83010000000002</v>
@@ -913,7 +913,7 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>-640.83010000000002</v>
@@ -936,7 +936,7 @@
         <v>5</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>-640.83010000000002</v>
@@ -959,7 +959,7 @@
         <v>5</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>-640.83010000000002</v>
@@ -982,7 +982,7 @@
         <v>5</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>-640.83010000000002</v>
@@ -1005,7 +1005,7 @@
         <v>5</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>-640.83010000000002</v>
@@ -1028,7 +1028,7 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>-640.83010000000002</v>

--- a/TextGame project/Assets/Resources/Story/4.xlsx
+++ b/TextGame project/Assets/Resources/Story/4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25483265-63B9-4999-9CA1-4BF98258B93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA1180F-8D5B-405B-9DE6-38655062EFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>旁白</t>
   </si>
@@ -220,6 +220,22 @@
   </si>
   <si>
     <t>（逞强）谁、谁怕了！走就走！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -837,8 +853,17 @@
       <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
-        <v>3</v>
+      <c r="C9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -883,8 +908,17 @@
       <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
-        <v>3</v>
+      <c r="C11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="R11">
         <v>5</v>
@@ -952,8 +986,8 @@
       <c r="B14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>3</v>
+      <c r="C14" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="R14">
         <v>5</v>
@@ -998,8 +1032,17 @@
       <c r="B16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
-        <v>3</v>
+      <c r="C16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="R16">
         <v>5</v>
